--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -413,294 +413,815 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>code</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>product_name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>brands</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>body</t>
+          <t>nutriscore_grade</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>energy_kcal_100g</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sugars_100g</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>proteins_100g</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>6111246721261</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fromage Blanc Nature</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sunt aut facere repellat provident occaecati excepturi optio reprehenderit</t>
+          <t>Milky Food Professional</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>quia et suscipit
-suscipit recusandae consequuntur expedita et cum
-reprehenderit molestiae ut ut quas totam
-nostrum rerum est autem sunt rem eveniet architecto</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-08-31 23:00:24</t>
-        </is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6111035000430</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sidi Ali</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>qui est esse</t>
+          <t>سيدي علي</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>est rerum tempore vitae
-sequi sint nihil reprehenderit dolor beatae ea dolores neque
-fugiat blanditiis voluptate porro vel nihil molestiae ut reiciendis
-qui aperiam non debitis possimus qui neque nisi nulla</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-31 23:00:24</t>
-        </is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6111242100992</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Perly</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Jaouda</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>97</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6111035000058</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Eau minérale naturelle</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sidi ali</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6111035002175</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sidi Ali</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sidi Ali</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6111266962187</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lait de la ferme jaouda</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jaouda</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>45</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6111242106949</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jben</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Jaouda</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>235</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3274080005003</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>isabelle</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cristaline</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7622210449283</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Prince</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LU, Mondelez Schweiz GmbH</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>466</v>
+      </c>
+      <c r="F10" t="n">
+        <v>32</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6111242101180</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>uht jaouda 1L</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Jaouda</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>58</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ea molestias quasi exercitationem repellat qui ipsa sit aut</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>et iusto sed quo iure
-voluptatem occaecati omnis eligendi aut ad
-voluptatem doloribus vel accusantium quis pariatur
-molestiae porro eius odio et labore et velit aut</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-31 23:00:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>eum et est occaecati</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ullam et saepe reiciendis voluptatem adipisci
-sit amet autem assumenda provident rerum culpa
-quis hic commodi nesciunt rem tenetur doloremque ipsam iure
-quis sunt voluptatem rerum illo velit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-31 23:00:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>nesciunt quas odio</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>repudiandae veniam quaerat sunt sed
-alias aut fugiat sit autem sed est
-voluptatem omnis possimus esse voluptatibus quis
-est aut tenetur dolor neque</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-31 23:00:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>dolorem eum magni eos aperiam quia</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ut aspernatur corporis harum nihil quis provident sequi
-mollitia nobis aliquid molestiae
-perspiciatis et ea nemo ab reprehenderit accusantium quas
-voluptate dolores velit et doloremque molestiae</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-31 23:00:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6111128000071</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ain Saïss</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Danone</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6111252421568</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>اكوافينا</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AQUAFINA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6111242100985</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Jaouda</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6111035000027</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6111035000027</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sidi Ali</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3760049790214</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pain De Mie Bio</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>La Boulangère, La Boulangère Bio</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>268</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6111246721278</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cream cheese</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>257</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6111035502828</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Eau minéral naturelle</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ain atlas</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3046920029759</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Excellence Noir Prodigieux 90% Cacao</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Lindt, Lindt &amp; Sprüngli</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>592</v>
+      </c>
+      <c r="F19" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>magnam facilis autem</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>dolore placeat quibusdam ea quo vitae
-magni quis enim qui quis quo nemo aut saepe
-quidem repellat excepturi ut quia
-sunt ut sequi eos ea sed quas</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-31 23:00:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>dolorem dolore est ipsam</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>dignissimos aperiam dolorem qui eum
-facilis quibusdam animi sint suscipit qui sint possimus cum
-quaerat magni maiores excepturi
-ipsam ut commodi dolor voluptatum modi aut vitae</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-31 23:00:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>nesciunt iure omnis dolorem tempora et accusantium</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>consectetur animi nesciunt iure dolore
-enim quia ad
-veniam autem ut quam aut nobis
-et est aut quod aut provident voluptas autem voluptas</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-31 23:00:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="G19" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>optio molestias id quia eum</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>quo et expedita modi cum officia vel magni
-doloribus qui repudiandae
-vero nisi sit
-quos veniam quod sed accusamus veritatis error</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-31 23:00:24</t>
-        </is>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5449000054227</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Coca-Cola Original Taste</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>COCA-COLA SERVICES SA/NV, Coca-Cola</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>42</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6111032009665</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Desconocido</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Salim</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>45</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3329770077003</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Skyr nature 0%</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Yoplait</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>57</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6111242100206</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Le nature</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Jaouda</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6111252421582</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>اكوافينا</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Aquafina</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3760049798609</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pain de mie grandes tranches Seigle &amp; Graines 500g</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>La boulangere, la Boulangère</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>297</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3168930010265</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>cruesly mélange de noix</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PEPSICO FRANCE, Quaker</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>462</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
